--- a/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de horas que duerme</t>
+          <t>Menores según del número de horas que duerme (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,38; 10,07</t>
+          <t>9,37; 10,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 9,68</t>
+          <t>9,06; 9,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 9,32</t>
+          <t>8,83; 9,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,63</t>
+          <t>9,22; 9,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,27</t>
+          <t>9,56; 10,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 10,44</t>
+          <t>9,33; 10,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,36</t>
+          <t>8,86; 9,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,06</t>
+          <t>9,58; 10,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,93</t>
+          <t>9,28; 9,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,23</t>
+          <t>8,91; 9,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 9,55</t>
+          <t>9,23; 9,55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,93</t>
+          <t>9,35; 9,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 10,53</t>
+          <t>9,82; 10,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,74</t>
+          <t>9,19; 9,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,4</t>
+          <t>9,06; 9,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,86</t>
+          <t>9,3; 9,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 10,59</t>
+          <t>9,95; 10,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,54</t>
+          <t>9,03; 9,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,32</t>
+          <t>8,89; 9,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,77</t>
+          <t>9,39; 9,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 10,45</t>
+          <t>9,99; 10,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,56</t>
+          <t>9,17; 9,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 9,3</t>
+          <t>9,03; 9,29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 10,09</t>
+          <t>9,47; 10,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 10,61</t>
+          <t>9,86; 10,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,62</t>
+          <t>8,96; 9,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 9,1</t>
+          <t>8,65; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,11</t>
+          <t>9,51; 10,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,42</t>
+          <t>9,61; 10,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 9,14</t>
+          <t>8,64; 9,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,05</t>
+          <t>9,55; 9,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 10,41</t>
+          <t>9,82; 10,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,45</t>
+          <t>8,96; 9,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,04</t>
+          <t>8,71; 9,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 10,06</t>
+          <t>9,5; 10,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 10,1</t>
+          <t>9,41; 10,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,39</t>
+          <t>9,58; 10,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,74</t>
+          <t>9,15; 9,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,91</t>
+          <t>9,44; 9,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 10,09</t>
+          <t>9,47; 10,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,87</t>
+          <t>9,3; 9,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,65</t>
+          <t>9,05; 9,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,93</t>
+          <t>9,54; 9,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,98</t>
+          <t>9,53; 9,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,98</t>
+          <t>9,52; 10,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,57</t>
+          <t>9,16; 9,58</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,97</t>
+          <t>9,3; 9,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 9,77</t>
+          <t>9,15; 9,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,31</t>
+          <t>9,66; 10,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,34</t>
+          <t>8,93; 9,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 10,24</t>
+          <t>9,31; 10,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,55</t>
+          <t>8,91; 9,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 10,39</t>
+          <t>9,73; 10,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,23</t>
+          <t>8,89; 9,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,92</t>
+          <t>9,39; 9,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,57</t>
+          <t>9,1; 9,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 10,23</t>
+          <t>9,77; 10,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 9,26</t>
+          <t>8,97; 9,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,37 +1416,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 10,03</t>
+          <t>9,35; 10,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,56</t>
+          <t>9,6; 10,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,59</t>
+          <t>9,19; 9,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 8,92</t>
+          <t>8,54; 8,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,9</t>
+          <t>9,28; 9,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,33</t>
+          <t>9,49; 10,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,79</t>
+          <t>9,23; 9,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,84</t>
+          <t>9,39; 9,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,25</t>
+          <t>9,64; 10,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,64</t>
+          <t>9,27; 9,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,77</t>
+          <t>9,36; 9,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,16</t>
+          <t>9,61; 10,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,78</t>
+          <t>9,37; 9,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 8,95</t>
+          <t>8,6; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 9,92</t>
+          <t>9,48; 9,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 10,13</t>
+          <t>9,62; 10,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,84</t>
+          <t>9,38; 9,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 8,85</t>
+          <t>8,5; 8,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,77</t>
+          <t>9,48; 9,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 10,05</t>
+          <t>9,7; 10,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,73</t>
+          <t>9,43; 9,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 8,84</t>
+          <t>8,57; 8,84</t>
         </is>
       </c>
     </row>
@@ -1696,42 +1696,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,79</t>
+          <t>9,35; 9,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,74</t>
+          <t>9,39; 9,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,06</t>
+          <t>9,73; 10,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 9,53</t>
+          <t>9,24; 9,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,73</t>
+          <t>9,31; 9,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,82</t>
+          <t>9,45; 9,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,63; 9,98</t>
+          <t>9,61; 9,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,56</t>
+          <t>9,3; 9,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,72</t>
+          <t>9,47; 9,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,96</t>
+          <t>9,72; 9,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,5</t>
+          <t>9,31; 9,51</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,71</t>
+          <t>9,53; 9,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,91</t>
+          <t>9,68; 9,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1851,47 +1851,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,07; 9,21</t>
+          <t>9,06; 9,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,73</t>
+          <t>9,55; 9,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,93</t>
+          <t>9,71; 9,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,6</t>
+          <t>9,41; 9,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,16</t>
+          <t>8,99; 9,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 9,7</t>
+          <t>9,56; 9,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,88</t>
+          <t>9,73; 9,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,62</t>
+          <t>9,49; 9,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,05; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 10,06</t>
+          <t>9,39; 10,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,69</t>
+          <t>9,03; 9,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 9,31</t>
+          <t>8,81; 9,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 9,62</t>
+          <t>9,23; 9,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,32</t>
+          <t>9,59; 10,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 10,37</t>
+          <t>9,31; 10,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,35</t>
+          <t>8,86; 9,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,6</t>
+          <t>9,1; 9,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,05</t>
+          <t>9,59; 10,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,88</t>
+          <t>9,29; 9,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,27</t>
+          <t>8,91; 9,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,55</t>
+          <t>9,23; 9,54</t>
         </is>
       </c>
     </row>
@@ -856,57 +856,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 9,9</t>
+          <t>9,33; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 10,5</t>
+          <t>9,81; 10,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,77</t>
+          <t>9,21; 9,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,41</t>
+          <t>9,06; 9,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,86</t>
+          <t>9,32; 9,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 10,6</t>
+          <t>9,99; 10,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,57</t>
+          <t>9,03; 9,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,31</t>
+          <t>8,9; 9,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,78</t>
+          <t>9,38; 9,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 10,47</t>
+          <t>9,99; 10,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 9,55</t>
+          <t>9,19; 9,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 10,09</t>
+          <t>9,47; 10,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 10,62</t>
+          <t>9,9; 10,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,67</t>
+          <t>8,95; 9,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 10,17</t>
+          <t>9,48; 10,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,41</t>
+          <t>9,62; 10,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 9,15</t>
+          <t>8,64; 9,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,99</t>
+          <t>9,56; 9,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 10,39</t>
+          <t>9,83; 10,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,42</t>
+          <t>8,99; 9,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,05</t>
+          <t>8,71; 9,06</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 10,05</t>
+          <t>9,51; 10,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 10,13</t>
+          <t>9,39; 10,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,36</t>
+          <t>9,58; 10,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,7</t>
+          <t>9,16; 9,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,88</t>
+          <t>9,46; 9,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 10,07</t>
+          <t>9,47; 10,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,86</t>
+          <t>9,26; 9,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,63</t>
+          <t>9,07; 9,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,91</t>
+          <t>9,56; 9,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,96</t>
+          <t>9,51; 9,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 10,0</t>
+          <t>9,52; 9,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,58</t>
+          <t>9,15; 9,56</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,9</t>
+          <t>9,35; 9,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,76</t>
+          <t>9,18; 9,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 10,3</t>
+          <t>9,67; 10,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,36</t>
+          <t>8,94; 9,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 10,2</t>
+          <t>9,29; 10,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,62</t>
+          <t>8,89; 9,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,46</t>
+          <t>9,73; 10,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,21</t>
+          <t>8,9; 9,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,93</t>
+          <t>9,38; 9,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,55</t>
+          <t>9,12; 9,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 10,28</t>
+          <t>9,76; 10,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,25</t>
+          <t>8,99; 9,24</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 10,02</t>
+          <t>9,35; 10,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,5</t>
+          <t>9,61; 10,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,58</t>
+          <t>9,18; 9,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,87</t>
+          <t>9,26; 9,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,49; 10,38</t>
+          <t>9,49; 10,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,78</t>
+          <t>9,21; 9,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,57; 8,89</t>
+          <t>8,58; 8,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,86</t>
+          <t>9,37; 9,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,62</t>
+          <t>9,29; 9,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,77</t>
+          <t>9,38; 9,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,13</t>
+          <t>9,62; 10,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,76</t>
+          <t>9,37; 9,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 8,94</t>
+          <t>8,59; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,92</t>
+          <t>9,48; 9,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,13</t>
+          <t>9,65; 10,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,83</t>
+          <t>9,39; 9,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 8,88</t>
+          <t>8,48; 8,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,76</t>
+          <t>9,49; 9,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 10,03</t>
+          <t>9,7; 10,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,73</t>
+          <t>9,42; 9,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 8,84</t>
+          <t>8,58; 8,85</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,35; 9,8</t>
+          <t>9,34; 9,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,52 +1706,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,08</t>
+          <t>9,73; 10,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,54</t>
+          <t>9,25; 9,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,73</t>
+          <t>9,34; 9,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,81</t>
+          <t>9,47; 9,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,61; 9,98</t>
+          <t>9,64; 9,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,56</t>
+          <t>9,31; 9,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 9,69</t>
+          <t>9,39; 9,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,71</t>
+          <t>9,46; 9,7</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,97</t>
+          <t>9,73; 9,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,51</t>
+          <t>9,31; 9,5</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 9,9</t>
+          <t>9,7; 9,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1851,37 +1851,37 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,21</t>
+          <t>9,07; 9,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,74</t>
+          <t>9,55; 9,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,92</t>
+          <t>9,71; 9,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,61</t>
+          <t>9,42; 9,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,15</t>
+          <t>9,0; 9,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,7</t>
+          <t>9,57; 9,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,88</t>
+          <t>9,73; 9,89</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,05; 9,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9,68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,09</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,68</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,06</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,92</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,09</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,34</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,35</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 10,11</t>
+          <t>9,59; 10,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,68</t>
+          <t>9,32; 10,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 9,3</t>
+          <t>8,86; 9,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,63</t>
+          <t>9,08; 9,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,34</t>
+          <t>9,38; 10,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 10,42</t>
+          <t>9,08; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,34</t>
+          <t>8,84; 9,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 9,58</t>
+          <t>9,18; 9,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,09</t>
+          <t>9,58; 10,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,91</t>
+          <t>9,28; 9,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,25</t>
+          <t>8,91; 9,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,54</t>
+          <t>9,18; 9,51</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,26</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,26</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,14</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,45</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,26</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,29</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,91</t>
+          <t>9,31; 9,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 10,51</t>
+          <t>9,96; 10,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,78</t>
+          <t>9,05; 9,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,42</t>
+          <t>8,86; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,85</t>
+          <t>9,33; 9,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 10,62</t>
+          <t>9,84; 10,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,56</t>
+          <t>9,21; 9,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,31</t>
+          <t>9,13; 9,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,77</t>
+          <t>9,39; 9,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 10,46</t>
+          <t>9,97; 10,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,56</t>
+          <t>9,18; 9,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,29</t>
+          <t>9,02; 9,3</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,95</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,12</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,81</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,26</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,86</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,95</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,82</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 10,06</t>
+          <t>9,54; 10,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 10,64</t>
+          <t>9,61; 10,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 9,65</t>
+          <t>8,87; 9,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 9,11</t>
+          <t>8,63; 9,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 10,11</t>
+          <t>9,46; 10,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,43</t>
+          <t>9,88; 10,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 9,44</t>
+          <t>8,95; 9,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 9,12</t>
+          <t>8,65; 9,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,99</t>
+          <t>9,58; 10,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 10,38</t>
+          <t>9,82; 10,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,06</t>
+          <t>8,68; 8,99</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,56</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,67</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>9,32</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 10,07</t>
+          <t>9,46; 9,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>9,47; 10,09</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9,3; 9,87</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9,0; 9,61</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,5; 10,06</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>9,39; 10,1</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,58; 10,33</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,16; 9,71</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,89</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 10,08</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,85</t>
+          <t>9,56; 10,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 9,65</t>
+          <t>9,11; 9,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,92</t>
+          <t>9,55; 9,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 9,96</t>
+          <t>9,53; 9,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,97</t>
+          <t>9,48; 9,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,56</t>
+          <t>9,12; 9,52</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10,01</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,03</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,93</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,17</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,06</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1276,52 +1276,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 9,96</t>
+          <t>9,3; 10,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,75</t>
+          <t>8,91; 9,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 10,32</t>
+          <t>9,71; 10,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,34</t>
+          <t>8,86; 9,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 10,15</t>
+          <t>9,33; 9,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,59</t>
+          <t>9,14; 9,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,41</t>
+          <t>9,64; 10,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,23</t>
+          <t>8,94; 9,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 9,92</t>
+          <t>9,39; 9,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 9,56</t>
+          <t>9,11; 9,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,24</t>
+          <t>8,96; 9,23</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,87</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,49</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,69</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9,63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10,0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9,39</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,87</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>8,68</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>9,25; 9,9</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9,45; 10,33</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9,21; 9,79</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8,55; 8,85</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>9,35; 10,03</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9,61; 10,48</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 9,6</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>8,54; 8,93</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9,26; 9,92</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,49; 10,37</t>
+          <t>9,62; 10,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,78</t>
+          <t>9,18; 9,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 8,89</t>
+          <t>8,49; 8,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 9,82</t>
+          <t>9,39; 9,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,26</t>
+          <t>9,64; 10,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,62</t>
+          <t>9,29; 9,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 8,85</t>
+          <t>8,57; 8,8</t>
         </is>
       </c>
     </row>
@@ -1488,54 +1488,54 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,69</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,67</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>9,56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,87</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9,57</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,69</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8,72</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>9,86</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>9,57</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,71</t>
+          <t>8,7</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9,5; 9,92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9,66; 10,13</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9,38; 9,84</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8,46; 8,83</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9,38; 9,77</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 10,16</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 9,77</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8,59; 8,94</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,93</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 10,11</t>
+          <t>9,64; 10,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,83</t>
+          <t>9,39; 9,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 8,85</t>
+          <t>8,57; 8,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,78</t>
+          <t>9,48; 9,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 10,04</t>
+          <t>9,7; 10,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,74</t>
+          <t>9,44; 9,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 8,85</t>
+          <t>8,55; 8,81</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9,79</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9,39</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>9,55</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>9,54</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,39</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>9,36</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,76</t>
+          <t>9,34; 9,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,73</t>
+          <t>9,47; 9,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 10,07</t>
+          <t>9,63; 9,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,55</t>
+          <t>9,27; 9,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,74</t>
+          <t>9,36; 9,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,8</t>
+          <t>9,41; 9,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,64; 9,99</t>
+          <t>9,73; 10,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,57</t>
+          <t>9,18; 9,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,69</t>
+          <t>9,4; 9,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,7</t>
+          <t>9,46; 9,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,98</t>
+          <t>9,72; 9,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,5</t>
+          <t>9,27; 9,46</t>
         </is>
       </c>
     </row>
@@ -1768,62 +1768,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>9,62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9,79</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9,8</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1836,42 +1836,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,72</t>
+          <t>9,54; 9,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,7; 9,91</t>
+          <t>9,72; 9,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>9,42; 9,6</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>8,99; 9,14</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9,52; 9,71</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,91</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,21</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 9,75</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,71; 9,94</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,6</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,16</t>
+          <t>9,04; 9,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,89</t>
+          <t>9,72; 9,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,62</t>
+          <t>9,48; 9,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,15</t>
+          <t>9,03; 9,13</t>
         </is>
       </c>
     </row>
